--- a/data/trans_dic/P39A3_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,91; 93,89</t>
+          <t>89,73; 93,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,42; 91,44</t>
+          <t>87,56; 91,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,51; 92,17</t>
+          <t>89,29; 92,12</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,6; 96,51</t>
+          <t>90,61; 96,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,56; 92,66</t>
+          <t>89,83; 92,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,77; 94,87</t>
+          <t>90,7; 94,99</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,61; 92,93</t>
+          <t>87,35; 92,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,78; 96,51</t>
+          <t>90,0; 97,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,67; 94,54</t>
+          <t>89,9; 95,4</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,81; 93,22</t>
+          <t>89,72; 93,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,18; 91,63</t>
+          <t>65,43; 91,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,62; 91,77</t>
+          <t>74,58; 91,58</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,76; 93,69</t>
+          <t>90,85; 94,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,69; 91,78</t>
+          <t>82,87; 91,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,25; 92,12</t>
+          <t>86,62; 92,13</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 93,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>516394; 539241</t>
+          <t>515319; 538796</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>537867; 562550</t>
+          <t>538673; 562310</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1064796; 1096460</t>
+          <t>1062107; 1095876</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1875226</t>
+          <t>1875227</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1022906; 1089623</t>
+          <t>1022988; 1090210</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>806771; 834638</t>
+          <t>809198; 836279</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1842353; 1925591</t>
+          <t>1840937; 1928177</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>592554; 628539</t>
+          <t>590844; 628055</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>779180; 837581</t>
+          <t>781116; 843009</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1384798; 1460015</t>
+          <t>1388242; 1473242</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>790815; 820817</t>
+          <t>789975; 822123</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>679283; 940527</t>
+          <t>671595; 940025</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1499263; 1750011</t>
+          <t>1422127; 1746364</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2958826; 3054492</t>
+          <t>2961758; 3072985</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2820047; 3129949</t>
+          <t>2825987; 3129795</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5820202; 6145157</t>
+          <t>5778210; 6145238</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A3_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A3_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,73; 93,81</t>
+          <t>90,12; 93,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,56; 91,4</t>
+          <t>87,66; 91,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,29; 92,12</t>
+          <t>89,34; 92,19</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,61; 96,56</t>
+          <t>88,97; 92,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>89,83; 92,84</t>
+          <t>89,77; 92,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,7; 94,99</t>
+          <t>89,93; 92,31</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,35; 92,86</t>
+          <t>86,71; 91,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,0; 97,13</t>
+          <t>87,54; 91,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,9; 95,4</t>
+          <t>87,81; 91,15</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,72; 93,37</t>
+          <t>88,53; 92,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,43; 91,58</t>
+          <t>88,93; 92,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,58; 91,58</t>
+          <t>89,31; 91,81</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,85; 94,26</t>
+          <t>89,77; 91,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,87; 91,77</t>
+          <t>89,57; 91,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,62; 92,13</t>
+          <t>89,92; 91,27</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>528808</t>
+          <t>568278</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>551672</t>
+          <t>592730</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1080481</t>
+          <t>1161008</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>515319; 538796</t>
+          <t>555502; 578861</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>538673; 562310</t>
+          <t>579656; 604443</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1062107; 1095876</t>
+          <t>1141455; 1177852</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1052366</t>
+          <t>878237</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>822860</t>
+          <t>916806</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1875227</t>
+          <t>1795042</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1022988; 1090210</t>
+          <t>858781; 895739</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>809198; 836279</t>
+          <t>901072; 930328</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1840937; 1928177</t>
+          <t>1770595; 1817521</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>612459</t>
+          <t>685489</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>804738</t>
+          <t>691522</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1417198</t>
+          <t>1377011</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>590844; 628055</t>
+          <t>662062; 702106</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>781116; 843009</t>
+          <t>675928; 704994</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1388242; 1473242</t>
+          <t>1348510; 1399738</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>806740</t>
+          <t>846210</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>871091</t>
+          <t>939772</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1677831</t>
+          <t>1785982</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>789975; 822123</t>
+          <t>825646; 862485</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>671595; 940025</t>
+          <t>922189; 956261</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1422127; 1746364</t>
+          <t>1759078; 1808375</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3000375</t>
+          <t>2978214</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3050363</t>
+          <t>3140829</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6050738</t>
+          <t>6119043</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2961758; 3072985</t>
+          <t>2942361; 3011350</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2825987; 3129795</t>
+          <t>3111738; 3166450</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5778210; 6145238</t>
+          <t>6071379; 6162176</t>
         </is>
       </c>
     </row>
